--- a/Tareas Game Project.xlsx
+++ b/Tareas Game Project.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MSI-GF75thin\Desktop\PRATICAS GITHUB(Sistemas 0483-Program 0485-Entorns 0487)\PRACTICAS\DINO_LLMM_U2_PF1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MSI-GF75thin\Desktop\PRATICAS GITHUB(Sistemas 0483-Program 0485-Entorns 0487)\DINO_LLMM_U2_PF1\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="25">
   <si>
     <t>TAREAS</t>
   </si>
@@ -83,13 +83,22 @@
     <t>CRASH</t>
   </si>
   <si>
-    <t>DETECTAR</t>
-  </si>
-  <si>
     <t>RESET</t>
   </si>
   <si>
     <t>BTN</t>
+  </si>
+  <si>
+    <t>MUSIC</t>
+  </si>
+  <si>
+    <t>ADD JUMP</t>
+  </si>
+  <si>
+    <t>ADD COIN</t>
+  </si>
+  <si>
+    <t>ADD G.OVER</t>
   </si>
 </sst>
 </file>
@@ -177,7 +186,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -202,17 +211,19 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -262,8 +273,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:D17" totalsRowShown="0">
-  <autoFilter ref="A1:D17"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:D20" totalsRowShown="0">
+  <autoFilter ref="A1:D20"/>
   <tableColumns count="4">
     <tableColumn id="1" name="TAREAS" dataDxfId="1"/>
     <tableColumn id="2" name="CHECKED"/>
@@ -537,26 +548,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="15.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="11"/>
+      <c r="E1" s="10"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
@@ -589,7 +600,7 @@
       <c r="B5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="14"/>
+      <c r="D5" s="12"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
@@ -598,16 +609,16 @@
       <c r="B6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="14"/>
+      <c r="D6" s="12"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="11" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="14"/>
+      <c r="C7" s="12"/>
       <c r="D7" s="4"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -617,11 +628,11 @@
       <c r="B8" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="15" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="3"/>
@@ -635,8 +646,8 @@
       <c r="B10" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
@@ -647,70 +658,87 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="11" t="s">
         <v>14</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
+      <c r="A14" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="14"/>
-      <c r="D14" s="15" t="s">
+      <c r="B14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" s="12"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="12"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="14"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="13" t="s">
+      <c r="C16" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="13"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="12"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
+      <c r="A18" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="12"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
+      <c r="A19" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="12"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Tareas Game Project.xlsx
+++ b/Tareas Game Project.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="24">
   <si>
     <t>TAREAS</t>
   </si>
@@ -84,9 +84,6 @@
   </si>
   <si>
     <t>RESET</t>
-  </si>
-  <si>
-    <t>BTN</t>
   </si>
   <si>
     <t>MUSIC</t>
@@ -203,9 +200,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
@@ -555,190 +551,191 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="10"/>
+      <c r="E1" s="9"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" s="12"/>
+      <c r="B5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="11"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" s="12"/>
+      <c r="B6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="11"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="12"/>
-      <c r="D7" s="4"/>
+      <c r="B7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="11"/>
+      <c r="D7" s="3"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
+      <c r="B8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
+      <c r="B10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
+      <c r="B12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
+      <c r="B13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C14" s="12"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="12"/>
+      <c r="B14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" s="11"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="11"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
+      <c r="B15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="B16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="12"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="11"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="12"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
+      <c r="D18" s="3"/>
+      <c r="E18" s="11"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D18" s="4"/>
-      <c r="E18" s="12"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
+      <c r="D19" s="3"/>
+      <c r="E19" s="11"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D19" s="4"/>
-      <c r="E19" s="12"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D20" s="4"/>
+      <c r="D20" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
